--- a/site/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,7 +1321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Contact Settings</t>
+          <t>Mailbox Settings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,19 +1331,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+          <t>h_01KQ7CSKGXGSV6NGD9Y3M94AZ6</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KQ7CSKGXGSV6NGD9Y3M94AZ6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mailbox Settings</t>
+          <t>OneDrive Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,19 +1353,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KQ7CSKGXGSV6NGD9Y3M94AZ6</t>
+          <t>h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KQ7CSKGXGSV6NGD9Y3M94AZ6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OneDrive Settings</t>
+          <t>Device Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,19 +1375,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+          <t>h_01KN1TCB7YSSTH14250DTZDD4F</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCB7YSSTH14250DTZDD4F</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Device Settings</t>
+          <t>Groups Settings</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1397,19 +1397,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KN1TCB7YSSTH14250DTZDD4F</t>
+          <t>h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCB7YSSTH14250DTZDD4F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Groups Settings</t>
+          <t>WriteBack Settings</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,63 +1419,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WriteBack Settings</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Business Groups</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Business Groups</t>
+          <t>Access Rules</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,41 +1485,41 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Access Rules</t>
+          <t>Organizational Unit (OU) Assignment Rules</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>h_01KMN29FF651PEW913V0D17KT4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN29FF651PEW913V0D17KT4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Organizational Unit (OU) Assignment Rules</t>
+          <t>Organisation Unit Employee (OU)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,63 +1529,63 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01KMN29FF651PEW913V0D17KT4</t>
+          <t>h_01KMQBXYNJ6DC2BYP73FRMAZAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN29FF651PEW913V0D17KT4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQBXYNJ6DC2BYP73FRMAZAN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Organisation Unit Employee (OU)</t>
+          <t>Monitoring Rules</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01KMQBXYNJ6DC2BYP73FRMAZAN</t>
+          <t>h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQBXYNJ6DC2BYP73FRMAZAN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Monitoring Rules</t>
+          <t>Monitoring Settings</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
+          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Monitoring Settings</t>
+          <t>Rule Detail (Monitoring)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1595,63 +1595,63 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Rule Detail (Monitoring)</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>h_01KMN40VMF41N5TF8FPZDF6A53</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN40VMF41N5TF8FPZDF6A53</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Naming Policy</t>
+          <t>Naming Policy Settings</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01KMN40VMF41N5TF8FPZDF6A53</t>
+          <t>h_01KMN45XQR7V20BD6R5JVQMJ92</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN40VMF41N5TF8FPZDF6A53</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN45XQR7V20BD6R5JVQMJ92</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Naming Policy Settings</t>
+          <t>Generate sAMAccountName</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01KMN45XQR7V20BD6R5JVQMJ92</t>
+          <t>h_01KMN4GEKY0M4KPDGR1EJ3FCH8</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN45XQR7V20BD6R5JVQMJ92</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN4GEKY0M4KPDGR1EJ3FCH8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Generate sAMAccountName</t>
+          <t>Generate UserPrincipalName (UPN)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1683,19 +1683,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01KMN4GEKY0M4KPDGR1EJ3FCH8</t>
+          <t>h_01KMN5EYC0AQNMA7FKB80GCRM2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN4GEKY0M4KPDGR1EJ3FCH8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC0AQNMA7FKB80GCRM2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Generate UserPrincipalName (UPN)</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,19 +1705,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01KMN5EYC0AQNMA7FKB80GCRM2</t>
+          <t>h_01KMN5EYC063KGS56YDE8Z6ATT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC0AQNMA7FKB80GCRM2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC063KGS56YDE8Z6ATT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Generate Email</t>
+          <t>Generate Common Name (CN)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,85 +1727,85 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01KMN5EYC063KGS56YDE8Z6ATT</t>
+          <t>h_01KMN5EYC0JTZT4ZY8TTQ7KCX9</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC063KGS56YDE8Z6ATT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC0JTZT4ZY8TTQ7KCX9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Generate Common Name (CN)</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01KMN5EYC0JTZT4ZY8TTQ7KCX9</t>
+          <t>h_01KMQNB8YFJHAQHKRTEZ19XQQE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC0JTZT4ZY8TTQ7KCX9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNB8YFJHAQHKRTEZ19XQQE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01KMQNB8YFJHAQHKRTEZ19XQQE</t>
+          <t>h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNB8YFJHAQHKRTEZ19XQQE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,85 +1815,85 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Operational Settings Definition</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Operational Settings Definition</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+          <t>h_01KN1ASDTRY0GR0850VZCFF8FP</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1ASDTRY0GR0850VZCFF8FP</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,41 +1903,41 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1947,41 +1947,41 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,32 +1991,10 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ADP-Workforce-Now-Microsoft-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
